--- a/Data/talleres.xlsx
+++ b/Data/talleres.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/geoworkshop/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{84FEF986-3621-40BD-A8EA-225A9AAF25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAB42109-BFF2-4669-B7D3-BC62036A2542}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{84FEF986-3621-40BD-A8EA-225A9AAF25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{386666D7-1CD9-41BA-9A8F-63C1CAEB8DAF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2581F85A-D1B6-4F42-AD35-348AD0B72821}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="190">
   <si>
     <t>-53.121693,-70.878428</t>
   </si>
@@ -582,6 +582,30 @@
   </si>
   <si>
     <t>=B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONA </t>
+  </si>
+  <si>
+    <t>NORTE GRANDE</t>
+  </si>
+  <si>
+    <t>NORTE CHICO</t>
+  </si>
+  <si>
+    <t>METROPOLITANA</t>
+  </si>
+  <si>
+    <t>CENTRO</t>
+  </si>
+  <si>
+    <t>SUR</t>
+  </si>
+  <si>
+    <t>EXTREMO SUR</t>
+  </si>
+  <si>
+    <t>METROPOLITANA ORIENTE</t>
   </si>
 </sst>
 </file>
@@ -603,12 +627,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -638,11 +668,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -977,19 +1008,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1ED25C-D677-4908-964F-893928947FC5}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="88.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" style="2"/>
+    <col min="4" max="4" width="88.7265625" customWidth="1"/>
+    <col min="5" max="5" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
@@ -1000,19 +1032,22 @@
         <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
@@ -1023,19 +1058,22 @@
         <v>98</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>106</v>
       </c>
@@ -1046,19 +1084,22 @@
         <v>94</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>107</v>
       </c>
@@ -1069,19 +1110,22 @@
         <v>90</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>108</v>
       </c>
@@ -1092,19 +1136,22 @@
         <v>86</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -1115,42 +1162,48 @@
         <v>82</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>111</v>
       </c>
@@ -1161,19 +1214,22 @@
         <v>74</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>112</v>
       </c>
@@ -1184,19 +1240,22 @@
         <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>113</v>
       </c>
@@ -1207,19 +1266,22 @@
         <v>66</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>114</v>
       </c>
@@ -1230,20 +1292,23 @@
         <v>62</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
@@ -1254,19 +1319,22 @@
         <v>58</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>116</v>
       </c>
@@ -1277,42 +1345,48 @@
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>118</v>
       </c>
@@ -1323,19 +1397,22 @@
         <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>119</v>
       </c>
@@ -1346,19 +1423,22 @@
         <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>120</v>
       </c>
@@ -1369,19 +1449,22 @@
         <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>121</v>
       </c>
@@ -1392,19 +1475,22 @@
         <v>34</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>122</v>
       </c>
@@ -1415,19 +1501,22 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>123</v>
       </c>
@@ -1438,19 +1527,22 @@
         <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>124</v>
       </c>
@@ -1461,19 +1553,22 @@
         <v>22</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -1484,19 +1579,22 @@
         <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>126</v>
       </c>
@@ -1507,19 +1605,22 @@
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>127</v>
       </c>
@@ -1530,19 +1631,22 @@
         <v>10</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>128</v>
       </c>
@@ -1553,19 +1657,22 @@
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>129</v>
       </c>
@@ -1576,15 +1683,18 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>179</v>
       </c>
     </row>

--- a/Data/talleres.xlsx
+++ b/Data/talleres.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/geoworkshop/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_5C49C1E9B6AB8F24A061087D4DAB1B4778780222" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21D94F7D-2087-4C12-AE4C-055C3FFE43AD}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -895,8 +901,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,13 +939,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -977,7 +991,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1011,6 +1025,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1045,9 +1060,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1220,11 +1236,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="87.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1282,7 +1308,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1305,13 +1331,13 @@
         <v>238</v>
       </c>
       <c r="H3">
-        <v>-20.290655</v>
+        <v>-20.290655000000001</v>
       </c>
       <c r="I3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1334,13 +1360,13 @@
         <v>239</v>
       </c>
       <c r="H4">
-        <v>-22.442374</v>
+        <v>-22.442374000000001</v>
       </c>
       <c r="I4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1363,13 +1389,13 @@
         <v>240</v>
       </c>
       <c r="H5">
-        <v>-23.592085</v>
+        <v>-23.592085000000001</v>
       </c>
       <c r="I5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1398,7 +1424,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1421,13 +1447,13 @@
         <v>242</v>
       </c>
       <c r="H7">
-        <v>-29.991259</v>
+        <v>-29.991258999999999</v>
       </c>
       <c r="I7" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1450,13 +1476,13 @@
         <v>243</v>
       </c>
       <c r="H8">
-        <v>-33.120464</v>
+        <v>-33.120463999999998</v>
       </c>
       <c r="I8" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1485,7 +1511,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1508,13 +1534,13 @@
         <v>245</v>
       </c>
       <c r="H10">
-        <v>-33.2953</v>
+        <v>-33.295299999999997</v>
       </c>
       <c r="I10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1537,13 +1563,13 @@
         <v>246</v>
       </c>
       <c r="H11">
-        <v>-33.279487</v>
+        <v>-33.279487000000003</v>
       </c>
       <c r="I11" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1566,13 +1592,13 @@
         <v>247</v>
       </c>
       <c r="H12">
-        <v>-33.460754</v>
+        <v>-33.460754000000001</v>
       </c>
       <c r="I12" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1595,13 +1621,13 @@
         <v>248</v>
       </c>
       <c r="H13">
-        <v>-33.611992</v>
+        <v>-33.611992000000001</v>
       </c>
       <c r="I13" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1624,13 +1650,13 @@
         <v>249</v>
       </c>
       <c r="H14">
-        <v>-34.158275</v>
+        <v>-34.158275000000003</v>
       </c>
       <c r="I14" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1653,13 +1679,13 @@
         <v>250</v>
       </c>
       <c r="H15">
-        <v>-35.422032</v>
+        <v>-35.422032000000002</v>
       </c>
       <c r="I15" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1688,7 +1714,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1711,13 +1737,13 @@
         <v>252</v>
       </c>
       <c r="H17">
-        <v>-36.633245</v>
+        <v>-36.633245000000002</v>
       </c>
       <c r="I17" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1740,13 +1766,13 @@
         <v>253</v>
       </c>
       <c r="H18">
-        <v>-36.79978</v>
+        <v>-36.799779999999998</v>
       </c>
       <c r="I18" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1769,13 +1795,13 @@
         <v>254</v>
       </c>
       <c r="H19">
-        <v>-37.454364</v>
+        <v>-37.454363999999998</v>
       </c>
       <c r="I19" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1798,13 +1824,13 @@
         <v>255</v>
       </c>
       <c r="H20">
-        <v>-38.769042</v>
+        <v>-38.769041999999999</v>
       </c>
       <c r="I20" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1827,13 +1853,13 @@
         <v>256</v>
       </c>
       <c r="H21">
-        <v>-39.810453</v>
+        <v>-39.810453000000003</v>
       </c>
       <c r="I21" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1862,7 +1888,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1885,13 +1911,13 @@
         <v>258</v>
       </c>
       <c r="H23">
-        <v>-41.272228</v>
+        <v>-41.272227999999998</v>
       </c>
       <c r="I23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1914,13 +1940,13 @@
         <v>259</v>
       </c>
       <c r="H24">
-        <v>-42.450034</v>
+        <v>-42.450034000000002</v>
       </c>
       <c r="I24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1943,13 +1969,13 @@
         <v>260</v>
       </c>
       <c r="H25">
-        <v>-45.606495</v>
+        <v>-45.606495000000002</v>
       </c>
       <c r="I25" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1978,7 +2004,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2001,13 +2027,13 @@
         <v>262</v>
       </c>
       <c r="H27">
-        <v>4.811781</v>
+        <v>4.8117809999999999</v>
       </c>
       <c r="I27">
-        <v>-74.053087</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>-74.053087000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2030,13 +2056,13 @@
         <v>263</v>
       </c>
       <c r="H28">
-        <v>10.951436</v>
+        <v>10.951435999999999</v>
       </c>
       <c r="I28">
-        <v>-74.834428</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>-74.834428000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -2059,13 +2085,13 @@
         <v>264</v>
       </c>
       <c r="H29">
-        <v>7.116952</v>
+        <v>7.1169520000000004</v>
       </c>
       <c r="I29">
-        <v>-73.117199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>-73.117198999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -2088,13 +2114,13 @@
         <v>265</v>
       </c>
       <c r="H30">
-        <v>3.500185</v>
+        <v>3.5001850000000001</v>
       </c>
       <c r="I30">
-        <v>-76.520858</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>-76.520858000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -2117,13 +2143,13 @@
         <v>266</v>
       </c>
       <c r="H31">
-        <v>6.157678</v>
+        <v>6.1576779999999998</v>
       </c>
       <c r="I31">
-        <v>-75.643388</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>-75.643388000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2146,13 +2172,13 @@
         <v>267</v>
       </c>
       <c r="H32">
-        <v>5.805998</v>
+        <v>5.8059979999999998</v>
       </c>
       <c r="I32">
-        <v>-73.032251</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>-73.032251000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2172,13 +2198,13 @@
         <v>216</v>
       </c>
       <c r="H33">
-        <v>-12.211562</v>
+        <v>-12.211562000000001</v>
       </c>
       <c r="I33">
-        <v>-77.040063</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>-77.040063000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2198,13 +2224,13 @@
         <v>217</v>
       </c>
       <c r="H34">
-        <v>-12.332937</v>
+        <v>-12.332936999999999</v>
       </c>
       <c r="I34">
-        <v>-77.061688</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>-77.061688000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2224,13 +2250,13 @@
         <v>218</v>
       </c>
       <c r="H35">
-        <v>-12.044313</v>
+        <v>-12.044313000000001</v>
       </c>
       <c r="I35">
-        <v>-77.12831300000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>-77.128313000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2253,10 +2279,10 @@
         <v>-16.409813</v>
       </c>
       <c r="I36">
-        <v>-71.535062</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>-71.535061999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2276,13 +2302,13 @@
         <v>220</v>
       </c>
       <c r="H37">
-        <v>-7.173188</v>
+        <v>-7.1731879999999997</v>
       </c>
       <c r="I37">
-        <v>-78.542438</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>-78.542438000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2302,13 +2328,13 @@
         <v>221</v>
       </c>
       <c r="H38">
-        <v>-10.981813</v>
+        <v>-10.981813000000001</v>
       </c>
       <c r="I38">
-        <v>-76.308063</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>-76.308063000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2328,13 +2354,13 @@
         <v>222</v>
       </c>
       <c r="H39">
-        <v>-6.762437</v>
+        <v>-6.7624370000000003</v>
       </c>
       <c r="I39">
-        <v>-79.835188</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>-79.835188000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2354,13 +2380,13 @@
         <v>223</v>
       </c>
       <c r="H40">
-        <v>-13.504188</v>
+        <v>-13.504187999999999</v>
       </c>
       <c r="I40">
-        <v>-71.980688</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>-71.980688000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2380,13 +2406,13 @@
         <v>224</v>
       </c>
       <c r="H41">
-        <v>-12.071938</v>
+        <v>-12.071937999999999</v>
       </c>
       <c r="I41">
-        <v>-75.275937</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>-75.275936999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2406,13 +2432,13 @@
         <v>225</v>
       </c>
       <c r="H42">
-        <v>-9.547062</v>
+        <v>-9.5470620000000004</v>
       </c>
       <c r="I42">
-        <v>-77.50806300000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>-77.508063000000007</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2435,10 +2461,10 @@
         <v>-15.559313</v>
       </c>
       <c r="I43">
-        <v>-69.73343800000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>-69.733438000000007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2458,13 +2484,13 @@
         <v>227</v>
       </c>
       <c r="H44">
-        <v>-5.017437</v>
+        <v>-5.0174370000000001</v>
       </c>
       <c r="I44">
-        <v>-80.638813</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>-80.638812999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2484,13 +2510,13 @@
         <v>228</v>
       </c>
       <c r="H45">
-        <v>-8.130813</v>
+        <v>-8.1308129999999998</v>
       </c>
       <c r="I45">
-        <v>-79.024187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>-79.024186999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2510,13 +2536,13 @@
         <v>229</v>
       </c>
       <c r="H46">
-        <v>-17.396937</v>
+        <v>-17.396937000000001</v>
       </c>
       <c r="I46">
-        <v>-70.460188</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>-70.460188000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2536,13 +2562,13 @@
         <v>230</v>
       </c>
       <c r="H47">
-        <v>-25.329313</v>
+        <v>-25.329312999999999</v>
       </c>
       <c r="I47">
         <v>-57.633063</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2565,10 +2591,10 @@
         <v>-25.327562</v>
       </c>
       <c r="I48">
-        <v>-57.636313</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>-57.636313000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2591,10 +2617,10 @@
         <v>-25.329563</v>
       </c>
       <c r="I49">
-        <v>-57.632938</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>-57.632938000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2614,13 +2640,13 @@
         <v>233</v>
       </c>
       <c r="H50">
-        <v>-25.675812</v>
+        <v>-25.675812000000001</v>
       </c>
       <c r="I50">
-        <v>-54.734562</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>-54.734561999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2640,13 +2666,13 @@
         <v>234</v>
       </c>
       <c r="H51">
-        <v>-25.701937</v>
+        <v>-25.701937000000001</v>
       </c>
       <c r="I51">
-        <v>-54.728188</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>-54.728188000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2672,7 +2698,7 @@
         <v>-55.517688</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>60</v>
       </c>
